--- a/data_extactor/batch_10_fa/trimmed/batch_0069_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0069_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | امور اداری و دفتری</t>
+          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | سرعت ادراک | توجه انتخابی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | بازرسان، آزمون‌گران، سورت‌کنندگان، نمونه‌برداران و توزین‌کنندگان | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات تولیدی | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | کارمندان برنامه‌ریزی، کنترل تولید و پیگیری سفارش‌ها | کارمندان انبار، ورود و خروج کالا و موجودی | متصدیان چیدمان و جمع‌آوری سفارش‌ها در انبار</t>
+          <t>کارگران درجه‌بندی و تفکیک محصولات کشاورزی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>تشخیص گفتار | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | کارشناسان منابع انسانی | منشی‌ها و مسئولان دفاتر حقوقی | کارمندان امور دفتری و عمومی | کارشناسان مدیریت پروژه | منشی‌ها و دستیاران اداری، به جز حوزه‌های حقوقی، پزشکی و اجرایی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان منابع انسانی | منشی‌ها و دستیاران اداری دفاتر حقوقی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان مدیریت پروژه | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | سخن گفتن | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | حقوق و امور دولتی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | ایمنی و امنیت عمومی</t>
+          <t>اداری | زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دادیاران، کارشناسان رسیدگی و مستشاران اداری | تندنویسان و ثبت‌کنندگان جلسات دادگاه و زیرنویس‌نویسان هم‌زمان | کارمندان دبیرخانه مراجع قضایی و صدور مجوز | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان بایگانی و ثبت اسناد | دستیاران پژوهشی قضایی و دفتریاران دادگاه | کارشناسان حقوقی و دستیاران وکالت</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | کارشناسان پژوهش و تحریر قضایی | کارشناسان و دستیاران امور حقوقی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری و دفتری | پزشکی و دندانپزشکی | رایانه و الکترونیک | مدیریت و امور اداری | علوم اقتصادی و حسابداری</t>
+          <t>خدمات مشتری و شخصی | اداری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورت‌حساب و محاسبات مالی | کارشناسان خدمات مشتریان | کارشناسان فناوری اطلاعات سلامت و ثبت‌کنندگان اسناد پزشکی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان اسناد و مدارک پزشکی | نمایندگان پیگیری حقوق بیماران | متصدیان پذیرش و کارمندان اطلاعات و راهنمایی</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان امور بیماران و پذیرش | متصدیان پذیرش و اطلاعات</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>اداری | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان خدمات مشتریان | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان بایگانی و ثبت اسناد | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | دستیاران منابع انسانی، به جز امور حقوق و دستمزد و ثبت زمان کار | کارمندان امور دفتری و عمومی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان خدمات و پشتیبانی مشتریان | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | امور اداری و دفتری | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی</t>
+          <t>زبان انگلیسی | اداری | خدمات مشتری و شخصی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | چابکی انگشتان | مرتب‌سازی اطلاعات | سرعت ادراک | توجه انتخابی | سرعت حرکت مچ و انگشتان دست</t>
+          <t>درک کتبی | بینایی نزدیک | مهارت انگشتان | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | سرعت مچ و انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارمندان حسابداری و حسابرسی | کارشناسان مدیریت اسناد و مدارک | کارمندان بایگانی و ثبت اسناد | کارشناسان اسناد و مدارک پزشکی | کارمندان امور دفتری و عمومی | کارمندان امور حقوق و دستمزد و ثبت زمان کار | کارشناسان تایپ و حروف‌چینی دیجیتال</t>
+          <t>کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | متصدیان امور دفتری و امور عمومی اداری | کارمندان امور حقوق، دستمزد و ثبت زمان | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | شنیدن فعال | نظارت | سخن گفتن</t>
+          <t>درک مطلب | نگارش | گوش دادن فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | درک شفاهی | بیان کتبی | سرعت حرکت مچ و انگشتان دست | مرتب‌سازی اطلاعات | چابکی انگشتان</t>
+          <t>بینایی نزدیک | درک کتبی | درک شفاهی | بیان کتبی | سرعت مچ و انگشتان | ترتیب‌دهی اطلاعات | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارمندان امور مکاتبات اداری | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | کارمندان بایگانی و ثبت اسناد | کارمندان امور دفتری و عمومی | نمونه‌خوانان و غلط‌گیران متون چاپی | منشی‌ها و دستیاران اداری، به جز حوزه‌های حقوقی، پزشکی و اجرایی</t>
+          <t>کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | متصدیان امور دفتری و امور عمومی اداری | ویراستاران فنی و نمونه‌خوان‌ها | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | مرتب‌سازی اطلاعات | ابتکار | تجسم فضایی | درک کتبی | روانی ایده‌ها | تشخیص رنگ‌های بصری</t>
+          <t>بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | تجسم | درک کتبی | روانی ایده‌ها | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران هنری | ویراستاران | طراحان گرافیک | تکنسین‌ها و کارگران لیتوگرافی و پیش‌ازچاپ | نمونه‌خوانان و غلط‌گیران متون چاپی | نویسندگان فنی و کارشناسان نگارش متون تخصصی | طراحان وب و رابط کاربری دیجیتال</t>
+          <t>مدیران هنری | ویراستاران | طراحان گرافیک | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | ویراستاران فنی و نمونه‌خوان‌ها | نویسندگان متون فنی | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری و دفتری | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | وضوح گفتار | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | وضوح گفتار | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورت‌حساب و محاسبات مالی | کارمندان حسابداری و حسابرسی | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان خدمات مشتریان | نمایندگان و کارشناسان فروش بیمه | پذیره‌نویسان و کارشناسان صدور بیمه | کارمندان امور دفتری و عمومی</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان خدمات و پشتیبانی مشتریان | نمایندگان و کارشناسان فروش بیمه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | چابکی انگشتان | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پیک‌ها و نامه‌رسانان | کارمندان بایگانی و ثبت اسناد | کارمندان امور دفتری و عمومی | کارمندان ثبت و پیگیری سفارش‌ها | متصدیان باجه‌های پستی | سورت‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌آلات تفکیک مرسولات پستی | کارمندان انبار، ورود و خروج کالا و موجودی</t>
+          <t>پیک‌ها و نامه‌رسان‌ها | متصدیان بایگانی و اسناد | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان باجه و امور پستی | اپراتورها و متصدیان تفکیک و پردازش پستی | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
